--- a/TestData.xlsx
+++ b/TestData.xlsx
@@ -19,57 +19,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>TestData1</t>
-  </si>
-  <si>
-    <t>TestData2</t>
-  </si>
-  <si>
-    <t>TestData3</t>
-  </si>
-  <si>
-    <t>TestData4</t>
-  </si>
-  <si>
-    <t>TestData5</t>
-  </si>
-  <si>
-    <t>TestData6</t>
-  </si>
-  <si>
-    <t>TestData7</t>
-  </si>
-  <si>
-    <t>TestData8</t>
-  </si>
-  <si>
-    <t>TestData9</t>
-  </si>
-  <si>
-    <t>TestData10</t>
-  </si>
-  <si>
-    <t>TestData11</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>Testcase</t>
   </si>
   <si>
-    <t>neo.assault@gmail.com</t>
-  </si>
-  <si>
-    <t>Welcome@1</t>
-  </si>
-  <si>
-    <t>Login</t>
-  </si>
-  <si>
-    <t>SearchProduct</t>
-  </si>
-  <si>
-    <t>Printed Dress</t>
+    <t>OrderProduct</t>
+  </si>
+  <si>
+    <t>OrderProductWithTwoUsers</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Creditcard</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Pratip</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>1111111111111111</t>
+  </si>
+  <si>
+    <t>05</t>
   </si>
 </sst>
 </file>
@@ -107,7 +98,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -128,6 +119,19 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -138,10 +142,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,80 +450,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
+      <c r="G3" s="2">
+        <v>2020</v>
       </c>
     </row>
   </sheetData>
